--- a/DataSet_85pag.xlsx
+++ b/DataSet_85pag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Florian\Desktop\TFG_benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59B75A7-EFAE-45EE-9FFF-281A4AEF37A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB231FE-DAAE-4988-BF31-C3CED3E1CF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="2325" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAG_Pinecone" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="196">
   <si>
     <t>ID</t>
   </si>
@@ -773,71 +773,194 @@
     <t>La respuesta generada correctamente indica que la información sobre la presión de los neumáticos no se encuentra en el manual de inyección electrónica, y proporciona detalles adicionales sobre el contenido del manual.</t>
   </si>
   <si>
-    <t>Tamaño del Documento</t>
-  </si>
-  <si>
-    <t>Tokens del PDF (Constante)</t>
-  </si>
-  <si>
-    <t>Input Tokens Reales (Fórmula en Excel)</t>
-  </si>
-  <si>
-    <t>10 Páginas</t>
-  </si>
-  <si>
-    <t>~4.700 tokens</t>
-  </si>
-  <si>
-    <t>4.700 + Input_Tokens_n8n</t>
-  </si>
-  <si>
-    <t>50 Páginas</t>
-  </si>
-  <si>
-    <t>~23.500 tokens</t>
-  </si>
-  <si>
-    <t>23.500 + Input_Tokens_n8n</t>
-  </si>
-  <si>
-    <t>100 Páginas</t>
-  </si>
-  <si>
-    <t>~47.000 tokens</t>
-  </si>
-  <si>
-    <t>47.000 + Input_Tokens_n8n</t>
-  </si>
-  <si>
-    <t>200 Páginas</t>
-  </si>
-  <si>
-    <t>~94.000 tokens</t>
-  </si>
-  <si>
-    <t>94.000 + Input_Tokens_n8n</t>
-  </si>
-  <si>
-    <t>300 Páginas</t>
-  </si>
-  <si>
-    <t>~141.000 tokens</t>
-  </si>
-  <si>
-    <t>(Ya tienes los datos reales del benchmark anterior)</t>
-  </si>
-  <si>
-    <t>&gt;total_text_tokens</t>
-  </si>
-  <si>
     <t>aprox PDF consume 36.000 tokens</t>
+  </si>
+  <si>
+    <t>Arquitectura</t>
+  </si>
+  <si>
+    <t>Coste Input (€)</t>
+  </si>
+  <si>
+    <t>Coste Output (€)</t>
+  </si>
+  <si>
+    <t>Coste Total (€)</t>
+  </si>
+  <si>
+    <t>RAG Pinecone</t>
+  </si>
+  <si>
+    <t>RAG Native</t>
+  </si>
+  <si>
+    <t>Long Context</t>
+  </si>
+  <si>
+    <r>
+      <t>RAG Pinecone (Tarifa OpenAI):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>(41.113 / 1.000.000 * 0.417056) + (4.616 / 1.000.000 * 2.681684) = 0,0171 € + 0,0124 € =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> 0,0295 €</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>RAG Native (Tarifa Gemini Flash):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">(328.623 / 1.000.000 * 0.42) + (10.004 / 1.000.000 * 0.05) = 0,1380 € + 0,0005 € = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0,1385 €</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Long Context (Tarifa Gemini Flash):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">(243.038 / 1.000.000 * 0.42) + (380 / 1.000.000 * 0.05) = 0,1020 € + 0,0001 € = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0,1021 €</t>
+    </r>
+  </si>
+  <si>
+    <t>&gt;coste total con 85 pag</t>
+  </si>
+  <si>
+    <t>coste factura= 0,27€ con 85pag + 0,20€ con 142 pag= 0,47€</t>
+  </si>
+  <si>
+    <r>
+      <t>Total Tokens Input(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tokens ajustados para que cuadre con Factura de Google Cloud</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total Tokens Output(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tokens ajustados para que cuadre con Factura de Google Cloud</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -857,6 +980,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -866,7 +1045,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -889,11 +1068,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -905,6 +1099,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1246,6 +1466,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>611034</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>38221</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5240C929-8E54-BE4C-9E08-4C6DF9506CE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11525250"/>
+          <a:ext cx="10278909" cy="866896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1444,15 +1713,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="5" max="5" width="48.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
     <col min="13" max="13" width="62.5703125" customWidth="1"/>
     <col min="14" max="14" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1499,7 +1770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1543,7 +1814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1587,7 +1858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1631,7 +1902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1675,7 +1946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1719,7 +1990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1763,7 +2034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1807,7 +2078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1851,7 +2122,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1895,7 +2166,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1939,7 +2210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1983,7 +2254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2027,7 +2298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2071,7 +2342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2115,7 +2386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2159,7 +2430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2203,7 +2474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2247,7 +2518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2291,7 +2562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2335,7 +2606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2378,6 +2649,18 @@
       <c r="O21" t="s">
         <v>51</v>
       </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="H23" s="2">
+        <f>SUM(H2:H21)</f>
+        <v>41113</v>
+      </c>
+      <c r="I23">
+        <f>SUM(I2:I21)</f>
+        <v>4616</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2386,10 +2669,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,7 +2720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2477,7 +2764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2521,7 +2808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2565,7 +2852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2609,7 +2896,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2653,7 +2940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2697,7 +2984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2741,7 +3028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2785,7 +3072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2829,7 +3116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2873,7 +3160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2917,7 +3204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2961,7 +3248,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3005,7 +3292,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3049,7 +3336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3093,7 +3380,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3137,7 +3424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3181,7 +3468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3225,7 +3512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3269,7 +3556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3312,6 +3599,18 @@
       <c r="N21" t="s">
         <v>20</v>
       </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="H23" s="2">
+        <f>SUM(H2:H21)</f>
+        <v>767691</v>
+      </c>
+      <c r="I23">
+        <f>SUM(I2:I21)</f>
+        <v>76664</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3320,17 +3619,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="35.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="13" max="13" width="90.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3374,7 +3677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="38.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3418,7 +3721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="63.75">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3462,7 +3765,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="25.5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3506,7 +3809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="25.5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3550,7 +3853,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="38.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3594,7 +3897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="25.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3638,7 +3941,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="38.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3682,7 +3985,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="25.5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3726,7 +4029,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="25.5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3770,7 +4073,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="38.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3814,7 +4117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="25.5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3858,7 +4161,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="25.5">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3902,7 +4205,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="25.5">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3946,7 +4249,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="25.5">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3990,7 +4293,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="25.5">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4034,7 +4337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4078,7 +4381,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="25.5">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4122,7 +4425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="38.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4166,7 +4469,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="25.5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4210,7 +4513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="38.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4254,93 +4557,141 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="H24">
+    <row r="24" spans="1:14">
+      <c r="B24" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="B25" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="B26" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="13.5" thickBot="1">
+      <c r="H29">
         <f>SUM(H2:H21)</f>
         <v>7759</v>
       </c>
-      <c r="I24">
+      <c r="I29">
         <f>SUM(I2:I21)</f>
         <v>2915</v>
       </c>
-      <c r="J24" s="2">
-        <f>H24+I24</f>
-        <v>10674</v>
-      </c>
-      <c r="K24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" ht="64.5" thickBot="1">
+      <c r="A30" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="26.25" thickBot="1">
+      <c r="A31" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="9">
+        <v>41113</v>
+      </c>
+      <c r="C31" s="9">
+        <v>4616</v>
+      </c>
+      <c r="D31" s="10">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1.24E-2</v>
+      </c>
+      <c r="F31" s="11">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C25" t="s">
-        <v>182</v>
-      </c>
-      <c r="D25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" t="s">
-        <v>186</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+    </row>
+    <row r="32" spans="1:14" ht="26.25" thickBot="1">
+      <c r="A32" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B32" s="9">
+        <v>328623</v>
+      </c>
+      <c r="C32" s="9">
+        <v>10004</v>
+      </c>
+      <c r="D32" s="10">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="E32" s="10">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F32" s="11">
+        <v>0.13850000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="26.25" thickBot="1">
+      <c r="A33" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>190</v>
-      </c>
-      <c r="C28" t="s">
-        <v>191</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="B33" s="9">
+        <v>243038</v>
+      </c>
+      <c r="C33" s="12">
+        <v>380</v>
+      </c>
+      <c r="D33" s="10">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1E-4</v>
+      </c>
+      <c r="F33" s="11">
+        <v>0.1021</v>
+      </c>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="G35" s="13">
+        <f>SUM(F31:F33)</f>
+        <v>0.27010000000000001</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+    <row r="36" spans="1:9">
+      <c r="G36" s="7"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="I39" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="C29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" t="s">
-        <v>197</v>
-      </c>
-      <c r="D30" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>